--- a/analysis/working/FitResults_17O.xlsx
+++ b/analysis/working/FitResults_17O.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kawecka/digios/analysis/working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC08127-B160-EB43-9C4A-6C9584CBEACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C41C7D3-FBFF-7D42-98D5-5162C19A3A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" xr2:uid="{A110777A-7F0B-7E4D-A346-2F5C12B69EB1}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="19760" windowHeight="17160" activeTab="1" xr2:uid="{A110777A-7F0B-7E4D-A346-2F5C12B69EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Separate peaks" sheetId="1" r:id="rId1"/>
+    <sheet name="Merged peaks" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="25">
   <si>
     <t>Ex</t>
   </si>
@@ -108,6 +109,9 @@
   </si>
   <si>
     <t>Int. corr * sin(x)dx * 180 / pi</t>
+  </si>
+  <si>
+    <t>Ex 3,53</t>
   </si>
 </sst>
 </file>
@@ -4709,15 +4713,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>608544</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>35982</xdr:rowOff>
+      <xdr:colOff>343961</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>110067</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>809627</xdr:colOff>
+      <xdr:colOff>545044</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>165099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4744,16 +4748,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>560918</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>21165</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>21168</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>42331</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>762001</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>150281</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>232835</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>171448</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6762,4 +6766,1294 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BA0B7A-CF02-3447-95C1-777BFCE48B4A}">
+  <dimension ref="B2:R46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>0.150836</v>
+      </c>
+      <c r="C4">
+        <f>B4-B4</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>4.9355599999999997</v>
+      </c>
+      <c r="E4">
+        <f>D4*4/4</f>
+        <v>4.9355599999999997</v>
+      </c>
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4">
+        <v>18.48</v>
+      </c>
+      <c r="L4">
+        <f>(K4+J4)/2</f>
+        <v>12.74</v>
+      </c>
+      <c r="M4">
+        <f>K4-J4</f>
+        <v>11.48</v>
+      </c>
+      <c r="N4">
+        <f>SIN(L4*$R$4)*M4</f>
+        <v>2.5316522797045882</v>
+      </c>
+      <c r="O4">
+        <f>E10</f>
+        <v>45.578699999999998</v>
+      </c>
+      <c r="P4">
+        <f>O4*N4</f>
+        <v>115.38941976097151</v>
+      </c>
+      <c r="R4">
+        <v>1.7453292499999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>19.97</v>
+      </c>
+      <c r="K5">
+        <v>25.09</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L8" si="0">(K5+J5)/2</f>
+        <v>22.53</v>
+      </c>
+      <c r="M5">
+        <f t="shared" ref="M5:M8" si="1">K5-J5</f>
+        <v>5.120000000000001</v>
+      </c>
+      <c r="N5">
+        <f>SIN(L5*$R$4)*M5</f>
+        <v>1.9618156629123236</v>
+      </c>
+      <c r="O5">
+        <f>E16</f>
+        <v>29.225300000000001</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:P8" si="2">O5*N5</f>
+        <v>57.334651293311531</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>26.16</v>
+      </c>
+      <c r="K6">
+        <v>30.2</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>28.18</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="1"/>
+        <v>4.0399999999999991</v>
+      </c>
+      <c r="N6">
+        <f>SIN(L6*$R$4)*M6</f>
+        <v>1.9078621347121447</v>
+      </c>
+      <c r="O6">
+        <f>E23</f>
+        <v>20.959299999999999</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="2"/>
+        <v>39.987454840072253</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>31.12</v>
+      </c>
+      <c r="K7">
+        <v>34.6</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>32.86</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="1"/>
+        <v>3.4800000000000004</v>
+      </c>
+      <c r="N7">
+        <f>SIN(L7*$R$4)*M7</f>
+        <v>1.8882067683873258</v>
+      </c>
+      <c r="O7">
+        <f>E31</f>
+        <v>14.080133333333334</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="2"/>
+        <v>26.586203059796002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>35.369999999999997</v>
+      </c>
+      <c r="K8">
+        <v>38.49</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>36.93</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="1"/>
+        <v>3.1200000000000045</v>
+      </c>
+      <c r="N8">
+        <f>SIN(L8*$R$4)*M8</f>
+        <v>1.8746172317238767</v>
+      </c>
+      <c r="O8">
+        <f>E41</f>
+        <v>7.8573733333333342</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="2"/>
+        <v>14.729567446754345</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>0.15763199999999999</v>
+      </c>
+      <c r="C9">
+        <f>B9-B$9</f>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>4.7452100000000002</v>
+      </c>
+      <c r="E9">
+        <f>D9*4/4</f>
+        <v>4.7452100000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" s="3">
+        <v>2.0922200000000002</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:C11" si="3">B10-B$9</f>
+        <v>1.9345880000000002</v>
+      </c>
+      <c r="D10">
+        <v>45.578699999999998</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ref="E10:E11" si="4">D10*4/4</f>
+        <v>45.578699999999998</v>
+      </c>
+      <c r="F10">
+        <f>N4</f>
+        <v>2.5316522797045882</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>3.4675099999999999</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="3"/>
+        <v>3.3098779999999999</v>
+      </c>
+      <c r="D11">
+        <v>4.7852399999999999</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="4"/>
+        <v>4.7852399999999999</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O11" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" t="s">
+        <v>11</v>
+      </c>
+      <c r="N12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14">
+        <v>11.38</v>
+      </c>
+      <c r="K14">
+        <v>19.93</v>
+      </c>
+      <c r="L14">
+        <v>15.65</v>
+      </c>
+      <c r="M14">
+        <f>K14-J14</f>
+        <v>8.5499999999999989</v>
+      </c>
+      <c r="N14">
+        <f>SIN(L14*$R$4)*M14</f>
+        <v>2.3064500153384562</v>
+      </c>
+      <c r="O14">
+        <f>E17</f>
+        <v>133.10599999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>21.33</v>
+      </c>
+      <c r="K15">
+        <v>26.32</v>
+      </c>
+      <c r="L15">
+        <v>23.82</v>
+      </c>
+      <c r="M15">
+        <f t="shared" ref="M15:M17" si="5">K15-J15</f>
+        <v>4.990000000000002</v>
+      </c>
+      <c r="N15">
+        <f t="shared" ref="N15:N17" si="6">SIN(L15*$R$4)*M15</f>
+        <v>2.0152846159773641</v>
+      </c>
+      <c r="O15">
+        <f>E24</f>
+        <v>83.522599999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B16" s="3">
+        <v>2.1246900000000002</v>
+      </c>
+      <c r="C16">
+        <f>B16-$B$9</f>
+        <v>1.9670580000000002</v>
+      </c>
+      <c r="D16">
+        <v>29.225300000000001</v>
+      </c>
+      <c r="E16">
+        <f>D16*4/4</f>
+        <v>29.225300000000001</v>
+      </c>
+      <c r="F16">
+        <f>N5</f>
+        <v>1.9618156629123236</v>
+      </c>
+      <c r="I16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16">
+        <v>27.41</v>
+      </c>
+      <c r="K16">
+        <v>31.42</v>
+      </c>
+      <c r="L16">
+        <v>29.42</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="5"/>
+        <v>4.0100000000000016</v>
+      </c>
+      <c r="N16">
+        <v>1.972</v>
+      </c>
+      <c r="O16">
+        <f>E32</f>
+        <v>46.512</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B17" s="4">
+        <v>3.6874799999999999</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ref="C17" si="7">B17-$B$9</f>
+        <v>3.5298479999999999</v>
+      </c>
+      <c r="D17">
+        <v>133.10599999999999</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:E26" si="8">D17*4/4</f>
+        <v>133.10599999999999</v>
+      </c>
+      <c r="F17">
+        <f>N14</f>
+        <v>2.3064500153384562</v>
+      </c>
+      <c r="I17" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>32.29</v>
+      </c>
+      <c r="K17">
+        <v>35.79</v>
+      </c>
+      <c r="L17">
+        <v>34.04</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="5"/>
+        <v>3.5</v>
+      </c>
+      <c r="N17">
+        <v>1.9552</v>
+      </c>
+      <c r="O17">
+        <f>E42</f>
+        <v>26.452933333333334</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B18" s="2">
+        <v>4.0610999999999997</v>
+      </c>
+      <c r="C18">
+        <f>B18-$B$9</f>
+        <v>3.9034679999999997</v>
+      </c>
+      <c r="D18">
+        <v>54.590899999999998</v>
+      </c>
+      <c r="E18">
+        <f>D18*4/4</f>
+        <v>54.590899999999998</v>
+      </c>
+      <c r="F18" t="str">
+        <f>N30</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B23" s="3">
+        <v>2.1393800000000001</v>
+      </c>
+      <c r="C23">
+        <f>B23-$B$9</f>
+        <v>1.9817480000000001</v>
+      </c>
+      <c r="D23">
+        <v>20.959299999999999</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="8"/>
+        <v>20.959299999999999</v>
+      </c>
+      <c r="F23">
+        <f>N6</f>
+        <v>1.9078621347121447</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B24" s="4">
+        <v>3.67523</v>
+      </c>
+      <c r="C24">
+        <f t="shared" ref="C24:C26" si="9">B24-$B$9</f>
+        <v>3.517598</v>
+      </c>
+      <c r="D24">
+        <v>83.522599999999997</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="8"/>
+        <v>83.522599999999997</v>
+      </c>
+      <c r="F24">
+        <f>N15</f>
+        <v>2.0152846159773641</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B25" s="2">
+        <v>4.03104</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="9"/>
+        <v>3.873408</v>
+      </c>
+      <c r="D25">
+        <v>30.095199999999998</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="8"/>
+        <v>30.095199999999998</v>
+      </c>
+      <c r="F25" t="str">
+        <f>N31</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B26" s="1">
+        <v>5.4665999999999997</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="9"/>
+        <v>5.3089680000000001</v>
+      </c>
+      <c r="D26">
+        <v>36.672199999999997</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="8"/>
+        <v>36.672199999999997</v>
+      </c>
+      <c r="F26" t="str">
+        <f>N39</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M29" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" t="s">
+        <v>16</v>
+      </c>
+      <c r="O29" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" t="s">
+        <v>11</v>
+      </c>
+      <c r="M30" t="s">
+        <v>11</v>
+      </c>
+      <c r="N30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B31" s="3">
+        <v>2.1854800000000001</v>
+      </c>
+      <c r="C31">
+        <f>B31-$B$9</f>
+        <v>2.0278480000000001</v>
+      </c>
+      <c r="D31">
+        <v>10.5601</v>
+      </c>
+      <c r="E31">
+        <f>D31*4/3</f>
+        <v>14.080133333333334</v>
+      </c>
+      <c r="F31">
+        <f>N7</f>
+        <v>1.8882067683873258</v>
+      </c>
+      <c r="I31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" t="s">
+        <v>11</v>
+      </c>
+      <c r="M31" t="s">
+        <v>11</v>
+      </c>
+      <c r="N31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B32" s="4">
+        <v>3.7056200000000001</v>
+      </c>
+      <c r="C32">
+        <f t="shared" ref="C32:C36" si="10">B32-$B$9</f>
+        <v>3.5479880000000001</v>
+      </c>
+      <c r="D32">
+        <v>34.884</v>
+      </c>
+      <c r="E32">
+        <f t="shared" ref="E32:E46" si="11">D32*4/3</f>
+        <v>46.512</v>
+      </c>
+      <c r="F32">
+        <f>N16</f>
+        <v>1.972</v>
+      </c>
+      <c r="I32" t="s">
+        <v>7</v>
+      </c>
+      <c r="J32">
+        <v>7</v>
+      </c>
+      <c r="K32">
+        <v>18.239999999999998</v>
+      </c>
+      <c r="L32">
+        <f t="shared" ref="L32:L35" si="12">(K32+J32)/2</f>
+        <v>12.62</v>
+      </c>
+      <c r="M32">
+        <f t="shared" ref="M32:M35" si="13">K32-J32</f>
+        <v>11.239999999999998</v>
+      </c>
+      <c r="N32">
+        <f>SIN(L32*$R$4)*M32</f>
+        <v>2.4557588906488061</v>
+      </c>
+      <c r="O32">
+        <f>E18</f>
+        <v>54.590899999999998</v>
+      </c>
+      <c r="P32">
+        <f t="shared" ref="P32:P35" si="14">O32*N32</f>
+        <v>134.06208802351992</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B33" s="2">
+        <v>4.0561499999999997</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="10"/>
+        <v>3.8985179999999997</v>
+      </c>
+      <c r="D33">
+        <v>17.899000000000001</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="11"/>
+        <v>23.865333333333336</v>
+      </c>
+      <c r="F33">
+        <f>N32</f>
+        <v>2.4557588906488061</v>
+      </c>
+      <c r="I33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33">
+        <v>19.8</v>
+      </c>
+      <c r="K33">
+        <v>25.17</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="12"/>
+        <v>22.484999999999999</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="13"/>
+        <v>5.370000000000001</v>
+      </c>
+      <c r="N33">
+        <f>SIN(L33*$R$4)*M33</f>
+        <v>2.0537111113807214</v>
+      </c>
+      <c r="O33">
+        <f>E25</f>
+        <v>30.095199999999998</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="14"/>
+        <v>61.806846639225085</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B34" s="1">
+        <v>5.4397200000000003</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="10"/>
+        <v>5.2820879999999999</v>
+      </c>
+      <c r="D34">
+        <v>23.372199999999999</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="11"/>
+        <v>31.162933333333331</v>
+      </c>
+      <c r="F34" t="str">
+        <f>N40</f>
+        <v>-</v>
+      </c>
+      <c r="I34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34">
+        <v>26.32</v>
+      </c>
+      <c r="K34">
+        <v>30.51</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="12"/>
+        <v>28.414999999999999</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="13"/>
+        <v>4.1900000000000013</v>
+      </c>
+      <c r="N34">
+        <f>SIN(L34*$R$4)*M34</f>
+        <v>1.9938302868190572</v>
+      </c>
+      <c r="O34">
+        <f>E33</f>
+        <v>23.865333333333336</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="14"/>
+        <v>47.58342440503241</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B35" s="6">
+        <v>6.4059999999999997</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="10"/>
+        <v>6.2483679999999993</v>
+      </c>
+      <c r="D35">
+        <v>2.69658</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="11"/>
+        <v>3.59544</v>
+      </c>
+      <c r="I35" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35">
+        <v>31.41</v>
+      </c>
+      <c r="K35">
+        <v>35.020000000000003</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="12"/>
+        <v>33.215000000000003</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="13"/>
+        <v>3.610000000000003</v>
+      </c>
+      <c r="N35">
+        <f>SIN(L35*$R$4)*M35</f>
+        <v>1.9774939894877259</v>
+      </c>
+      <c r="O35">
+        <f>E43</f>
+        <v>17.3916</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="14"/>
+        <v>34.391784467574738</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B36" s="7">
+        <v>7.1472600000000002</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="10"/>
+        <v>6.9896279999999997</v>
+      </c>
+      <c r="D36">
+        <v>7.5666200000000003</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="11"/>
+        <v>10.088826666666668</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="I38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" t="s">
+        <v>13</v>
+      </c>
+      <c r="M38" t="s">
+        <v>12</v>
+      </c>
+      <c r="N38" t="s">
+        <v>16</v>
+      </c>
+      <c r="O38" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>5</v>
+      </c>
+      <c r="J39" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" t="s">
+        <v>11</v>
+      </c>
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>6</v>
+      </c>
+      <c r="J40" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" t="s">
+        <v>11</v>
+      </c>
+      <c r="L40" t="s">
+        <v>11</v>
+      </c>
+      <c r="M40" t="s">
+        <v>11</v>
+      </c>
+      <c r="N40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B41" s="3">
+        <v>2.2074199999999999</v>
+      </c>
+      <c r="C41">
+        <f>B41-$B$9</f>
+        <v>2.0497879999999999</v>
+      </c>
+      <c r="D41">
+        <v>5.8930300000000004</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="11"/>
+        <v>7.8573733333333342</v>
+      </c>
+      <c r="F41">
+        <f>N8</f>
+        <v>1.8746172317238767</v>
+      </c>
+      <c r="I41" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" t="s">
+        <v>11</v>
+      </c>
+      <c r="M41" t="s">
+        <v>11</v>
+      </c>
+      <c r="N41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B42" s="4">
+        <v>3.7222499999999998</v>
+      </c>
+      <c r="C42">
+        <f t="shared" ref="C42:C46" si="15">B42-$B$9</f>
+        <v>3.5646179999999998</v>
+      </c>
+      <c r="D42">
+        <v>19.839700000000001</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="11"/>
+        <v>26.452933333333334</v>
+      </c>
+      <c r="F42">
+        <f>N17</f>
+        <v>1.9552</v>
+      </c>
+      <c r="I42" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42">
+        <v>11.93</v>
+      </c>
+      <c r="K42">
+        <v>20.37</v>
+      </c>
+      <c r="L42">
+        <f>(K42+J42)/2</f>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="M42">
+        <f>K42-J42</f>
+        <v>8.4400000000000013</v>
+      </c>
+      <c r="N42">
+        <f>SIN(L42*R$4)*M42</f>
+        <v>2.3476111957144932</v>
+      </c>
+      <c r="O42">
+        <f>E26</f>
+        <v>36.672199999999997</v>
+      </c>
+      <c r="P42">
+        <f t="shared" ref="P42:P44" si="16">O42*N42</f>
+        <v>86.09206729148103</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B43" s="2">
+        <v>4.0853200000000003</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="15"/>
+        <v>3.9276880000000003</v>
+      </c>
+      <c r="D43">
+        <v>13.043699999999999</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="11"/>
+        <v>17.3916</v>
+      </c>
+      <c r="F43" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I43" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43">
+        <v>21.86</v>
+      </c>
+      <c r="K43">
+        <v>26.94</v>
+      </c>
+      <c r="L43">
+        <f t="shared" ref="L43:L44" si="17">(K43+J43)/2</f>
+        <v>24.4</v>
+      </c>
+      <c r="M43">
+        <f t="shared" ref="M43:M44" si="18">K43-J43</f>
+        <v>5.0800000000000018</v>
+      </c>
+      <c r="N43">
+        <f>SIN(L43*R$4)*M43</f>
+        <v>2.098570501257452</v>
+      </c>
+      <c r="O43">
+        <f>E34</f>
+        <v>31.162933333333331</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="16"/>
+        <v>65.397612625985886</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B44" s="1">
+        <v>5.4534799999999999</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="15"/>
+        <v>5.2958479999999994</v>
+      </c>
+      <c r="D44">
+        <v>27.661000000000001</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="11"/>
+        <v>36.881333333333338</v>
+      </c>
+      <c r="F44" t="str">
+        <f>N41</f>
+        <v>-</v>
+      </c>
+      <c r="I44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44">
+        <v>27.99</v>
+      </c>
+      <c r="K44">
+        <v>32.090000000000003</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="17"/>
+        <v>30.04</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="18"/>
+        <v>4.100000000000005</v>
+      </c>
+      <c r="N44">
+        <f>SIN(L44*R$4)*M44</f>
+        <v>2.0524783572308563</v>
+      </c>
+      <c r="O44">
+        <f>E44</f>
+        <v>36.881333333333338</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="16"/>
+        <v>75.698138452483633</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B45" s="6">
+        <v>6.48271</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="15"/>
+        <v>6.3250779999999995</v>
+      </c>
+      <c r="D45">
+        <v>0.40249699999999999</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="11"/>
+        <v>0.53666266666666662</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B46" s="7">
+        <v>7.1</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="15"/>
+        <v>6.9423680000000001</v>
+      </c>
+      <c r="D46">
+        <v>2.4890400000000001</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="11"/>
+        <v>3.3187200000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>